--- a/artfynd/A 25774-2026 artfynd.xlsx
+++ b/artfynd/A 25774-2026 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134162456</v>
+        <v>134164225</v>
       </c>
       <c r="B2" t="n">
         <v>79359</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479228</v>
+        <v>479428</v>
       </c>
       <c r="R2" t="n">
-        <v>6723907</v>
+        <v>6723858</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134164225</v>
+        <v>134162456</v>
       </c>
       <c r="B3" t="n">
         <v>79359</v>
@@ -822,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479428</v>
+        <v>479228</v>
       </c>
       <c r="R3" t="n">
-        <v>6723858</v>
+        <v>6723907</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +862,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134165499</v>
+        <v>134165365</v>
       </c>
       <c r="B4" t="n">
-        <v>57972</v>
+        <v>79359</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -905,39 +905,34 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479354</v>
+        <v>479328</v>
       </c>
       <c r="R4" t="n">
-        <v>6724019</v>
+        <v>6723999</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -979,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1113,10 +1108,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134165365</v>
+        <v>134165499</v>
       </c>
       <c r="B6" t="n">
-        <v>79359</v>
+        <v>57972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1124,34 +1119,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479328</v>
+        <v>479354</v>
       </c>
       <c r="R6" t="n">
-        <v>6723999</v>
+        <v>6724019</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1183,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1770,7 +1770,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134164194</v>
+        <v>134165546</v>
       </c>
       <c r="B12" t="n">
         <v>79359</v>
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479427</v>
+        <v>479354</v>
       </c>
       <c r="R12" t="n">
-        <v>6723856</v>
+        <v>6723979</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,12 +1850,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1882,7 +1877,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134165546</v>
+        <v>134164194</v>
       </c>
       <c r="B13" t="n">
         <v>79359</v>
@@ -1917,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479354</v>
+        <v>479427</v>
       </c>
       <c r="R13" t="n">
-        <v>6723979</v>
+        <v>6723856</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1952,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1962,7 +1957,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,7 +1989,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134162699</v>
+        <v>134164387</v>
       </c>
       <c r="B14" t="n">
         <v>79359</v>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479239</v>
+        <v>479421</v>
       </c>
       <c r="R14" t="n">
-        <v>6723797</v>
+        <v>6723880</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,12 +2069,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2213,7 +2208,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134163607</v>
+        <v>134162699</v>
       </c>
       <c r="B16" t="n">
         <v>79359</v>
@@ -2248,10 +2243,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479323</v>
+        <v>479239</v>
       </c>
       <c r="R16" t="n">
-        <v>6723858</v>
+        <v>6723797</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2283,7 +2278,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2293,12 +2288,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2325,10 +2320,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134165684</v>
+        <v>134163607</v>
       </c>
       <c r="B17" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2336,21 +2331,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2360,10 +2355,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479369</v>
+        <v>479323</v>
       </c>
       <c r="R17" t="n">
-        <v>6723963</v>
+        <v>6723858</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2395,7 +2390,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2405,7 +2400,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:37</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2432,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134164387</v>
+        <v>134165684</v>
       </c>
       <c r="B18" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479421</v>
+        <v>479369</v>
       </c>
       <c r="R18" t="n">
-        <v>6723880</v>
+        <v>6723963</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2646,7 +2646,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134166446</v>
+        <v>134164406</v>
       </c>
       <c r="B20" t="n">
         <v>79359</v>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479281</v>
+        <v>479425</v>
       </c>
       <c r="R20" t="n">
-        <v>6723751</v>
+        <v>6723879</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,12 +2726,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Draperad tall.</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2865,7 +2860,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134165042</v>
+        <v>134166446</v>
       </c>
       <c r="B22" t="n">
         <v>79359</v>
@@ -2900,10 +2895,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479336</v>
+        <v>479281</v>
       </c>
       <c r="R22" t="n">
-        <v>6723933</v>
+        <v>6723751</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2935,7 +2930,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2945,12 +2940,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Gran</t>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2977,7 +2972,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134165230</v>
+        <v>134165042</v>
       </c>
       <c r="B23" t="n">
         <v>79359</v>
@@ -3012,10 +3007,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479282</v>
+        <v>479336</v>
       </c>
       <c r="R23" t="n">
-        <v>6723997</v>
+        <v>6723932</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3047,7 +3042,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3057,7 +3052,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,7 +3196,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134164406</v>
+        <v>134165321</v>
       </c>
       <c r="B25" t="n">
         <v>79359</v>
@@ -3231,10 +3231,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479425</v>
+        <v>479298</v>
       </c>
       <c r="R25" t="n">
-        <v>6723879</v>
+        <v>6724027</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3266,7 +3266,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3276,7 +3276,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3303,7 +3308,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134165321</v>
+        <v>134165230</v>
       </c>
       <c r="B26" t="n">
         <v>79359</v>
@@ -3338,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479298</v>
+        <v>479282</v>
       </c>
       <c r="R26" t="n">
-        <v>6724027</v>
+        <v>6723997</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3373,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3383,12 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3853,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134162425</v>
+        <v>134163619</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79359</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3864,21 +3864,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479228</v>
+        <v>479321</v>
       </c>
       <c r="R31" t="n">
-        <v>6723907</v>
+        <v>6723859</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4067,10 +4067,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134163619</v>
+        <v>134162425</v>
       </c>
       <c r="B33" t="n">
-        <v>79359</v>
+        <v>79116</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479321</v>
+        <v>479228</v>
       </c>
       <c r="R33" t="n">
-        <v>6723859</v>
+        <v>6723907</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4174,7 +4174,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134163648</v>
+        <v>134165466</v>
       </c>
       <c r="B34" t="n">
         <v>79359</v>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479322</v>
+        <v>479354</v>
       </c>
       <c r="R34" t="n">
-        <v>6723860</v>
+        <v>6724022</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4254,7 +4254,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4281,10 +4281,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134163276</v>
+        <v>134163648</v>
       </c>
       <c r="B35" t="n">
-        <v>79978</v>
+        <v>79359</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4292,21 +4292,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4316,10 +4316,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479265</v>
+        <v>479322</v>
       </c>
       <c r="R35" t="n">
-        <v>6723901</v>
+        <v>6723860</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4351,7 +4351,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4388,10 +4388,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134165466</v>
+        <v>134163276</v>
       </c>
       <c r="B36" t="n">
-        <v>79359</v>
+        <v>79978</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4399,21 +4399,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4423,10 +4423,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479354</v>
+        <v>479265</v>
       </c>
       <c r="R36" t="n">
-        <v>6724022</v>
+        <v>6723901</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4468,7 +4468,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4495,7 +4495,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134164460</v>
+        <v>134163625</v>
       </c>
       <c r="B37" t="n">
         <v>79359</v>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479403</v>
+        <v>479321</v>
       </c>
       <c r="R37" t="n">
-        <v>6723893</v>
+        <v>6723861</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4602,10 +4602,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134164890</v>
+        <v>134164460</v>
       </c>
       <c r="B38" t="n">
-        <v>79117</v>
+        <v>79359</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479390</v>
+        <v>479403</v>
       </c>
       <c r="R38" t="n">
-        <v>6723901</v>
+        <v>6723893</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4821,10 +4821,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134163625</v>
+        <v>134164890</v>
       </c>
       <c r="B40" t="n">
-        <v>79359</v>
+        <v>79117</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4832,21 +4832,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479321</v>
+        <v>479390</v>
       </c>
       <c r="R40" t="n">
-        <v>6723861</v>
+        <v>6723901</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4928,10 +4928,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134166742</v>
+        <v>134166374</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>79359</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4939,39 +4939,34 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479259</v>
+        <v>479313</v>
       </c>
       <c r="R41" t="n">
-        <v>6723740</v>
+        <v>6723769</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5003,7 +4998,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5013,12 +5008,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5045,10 +5035,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134166374</v>
+        <v>134166742</v>
       </c>
       <c r="B42" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5056,34 +5046,39 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479313</v>
+        <v>479259</v>
       </c>
       <c r="R42" t="n">
-        <v>6723769</v>
+        <v>6723740</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5115,7 +5110,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5125,7 +5120,12 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC42" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5259,10 +5259,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134164544</v>
+        <v>134166963</v>
       </c>
       <c r="B44" t="n">
-        <v>57972</v>
+        <v>79359</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5270,39 +5270,34 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P44" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479407</v>
+        <v>479288</v>
       </c>
       <c r="R44" t="n">
-        <v>6723892</v>
+        <v>6723786</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5334,7 +5329,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5344,12 +5339,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5376,10 +5366,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134166963</v>
+        <v>134166567</v>
       </c>
       <c r="B45" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5387,34 +5377,39 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479288</v>
+        <v>479256</v>
       </c>
       <c r="R45" t="n">
-        <v>6723786</v>
+        <v>6723737</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5446,7 +5441,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5456,7 +5451,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Bild koda.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5483,10 +5483,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134166567</v>
+        <v>134164544</v>
       </c>
       <c r="B46" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5494,16 +5494,16 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
@@ -5514,7 +5514,7 @@
       <c r="I46" t="inlineStr"/>
       <c r="M46" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -5523,10 +5523,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479256</v>
+        <v>479407</v>
       </c>
       <c r="R46" t="n">
-        <v>6723737</v>
+        <v>6723892</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5558,7 +5558,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5568,12 +5568,12 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Ringhack på tall. Bild koda.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5707,7 +5707,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134166463</v>
+        <v>134163583</v>
       </c>
       <c r="B48" t="n">
         <v>79359</v>
@@ -5742,10 +5742,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479262</v>
+        <v>479322</v>
       </c>
       <c r="R48" t="n">
-        <v>6723756</v>
+        <v>6723856</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5814,7 +5814,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134163583</v>
+        <v>134166463</v>
       </c>
       <c r="B49" t="n">
         <v>79359</v>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479322</v>
+        <v>479262</v>
       </c>
       <c r="R49" t="n">
-        <v>6723856</v>
+        <v>6723756</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5921,50 +5921,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134165483</v>
+        <v>134165072</v>
       </c>
       <c r="B50" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479354</v>
+        <v>479335</v>
       </c>
       <c r="R50" t="n">
-        <v>6724019</v>
+        <v>6723933</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5996,7 +5991,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6006,7 +6001,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6033,7 +6028,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134165072</v>
+        <v>134165087</v>
       </c>
       <c r="B51" t="n">
         <v>79359</v>
@@ -6068,7 +6063,7 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479335</v>
+        <v>479332</v>
       </c>
       <c r="R51" t="n">
         <v>6723933</v>
@@ -6140,45 +6135,50 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134165087</v>
+        <v>134165483</v>
       </c>
       <c r="B52" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479332</v>
+        <v>479354</v>
       </c>
       <c r="R52" t="n">
-        <v>6723933</v>
+        <v>6724019</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6247,45 +6247,50 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134162509</v>
+        <v>134166323</v>
       </c>
       <c r="B53" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479217</v>
+        <v>479371</v>
       </c>
       <c r="R53" t="n">
-        <v>6723843</v>
+        <v>6723757</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6317,7 +6322,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6327,12 +6332,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6359,7 +6359,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134163189</v>
+        <v>134167110</v>
       </c>
       <c r="B54" t="n">
         <v>79359</v>
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479248</v>
+        <v>479287</v>
       </c>
       <c r="R54" t="n">
-        <v>6723888</v>
+        <v>6723832</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6466,7 +6466,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134167110</v>
+        <v>134163189</v>
       </c>
       <c r="B55" t="n">
         <v>79359</v>
@@ -6501,10 +6501,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479287</v>
+        <v>479248</v>
       </c>
       <c r="R55" t="n">
-        <v>6723832</v>
+        <v>6723888</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6573,50 +6573,45 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134166323</v>
+        <v>134162509</v>
       </c>
       <c r="B56" t="n">
-        <v>8460</v>
+        <v>79359</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479371</v>
+        <v>479217</v>
       </c>
       <c r="R56" t="n">
-        <v>6723757</v>
+        <v>6723843</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6648,7 +6643,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6658,7 +6653,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 25774-2026 artfynd.xlsx
+++ b/artfynd/A 25774-2026 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>134164225</v>
+        <v>134162456</v>
       </c>
       <c r="B2" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479428</v>
+        <v>479228</v>
       </c>
       <c r="R2" t="n">
-        <v>6723858</v>
+        <v>6723907</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -745,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:04</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +755,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:04</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134162456</v>
+        <v>134164225</v>
       </c>
       <c r="B3" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479228</v>
+        <v>479428</v>
       </c>
       <c r="R3" t="n">
-        <v>6723907</v>
+        <v>6723858</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -852,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:04</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,12 +867,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:04</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,10 +894,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134165365</v>
+        <v>134164290</v>
       </c>
       <c r="B4" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -929,10 +929,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479328</v>
+        <v>479422</v>
       </c>
       <c r="R4" t="n">
-        <v>6723999</v>
+        <v>6723871</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,7 +964,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +974,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,10 +1001,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134164290</v>
+        <v>134165365</v>
       </c>
       <c r="B5" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1036,10 +1036,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479422</v>
+        <v>479328</v>
       </c>
       <c r="R5" t="n">
-        <v>6723871</v>
+        <v>6723999</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1223,7 +1223,7 @@
         <v>134165773</v>
       </c>
       <c r="B7" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1559,7 +1559,7 @@
         <v>134165540</v>
       </c>
       <c r="B10" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1666,7 +1666,7 @@
         <v>134165475</v>
       </c>
       <c r="B11" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1773,7 +1773,7 @@
         <v>134165546</v>
       </c>
       <c r="B12" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,7 +1880,7 @@
         <v>134164194</v>
       </c>
       <c r="B13" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1989,10 +1989,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134164387</v>
+        <v>134162699</v>
       </c>
       <c r="B14" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2024,10 +2024,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479421</v>
+        <v>479239</v>
       </c>
       <c r="R14" t="n">
-        <v>6723880</v>
+        <v>6723797</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2059,7 +2059,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,7 +2069,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2208,10 +2213,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134162699</v>
+        <v>134163607</v>
       </c>
       <c r="B16" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2243,10 +2248,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479239</v>
+        <v>479323</v>
       </c>
       <c r="R16" t="n">
-        <v>6723797</v>
+        <v>6723858</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2278,7 +2283,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2288,12 +2293,12 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2320,10 +2325,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134163607</v>
+        <v>134165684</v>
       </c>
       <c r="B17" t="n">
-        <v>79359</v>
+        <v>79985</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2331,21 +2336,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2355,10 +2360,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479323</v>
+        <v>479369</v>
       </c>
       <c r="R17" t="n">
-        <v>6723858</v>
+        <v>6723963</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2390,7 +2395,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2400,12 +2405,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>11:37</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2432,10 +2432,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134165684</v>
+        <v>134164387</v>
       </c>
       <c r="B18" t="n">
-        <v>79978</v>
+        <v>79366</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2443,21 +2443,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2467,10 +2467,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479369</v>
+        <v>479421</v>
       </c>
       <c r="R18" t="n">
-        <v>6723963</v>
+        <v>6723880</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,7 +2502,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2512,7 +2512,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2542,7 +2542,7 @@
         <v>134163059</v>
       </c>
       <c r="B19" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2646,10 +2646,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134164406</v>
+        <v>134166446</v>
       </c>
       <c r="B20" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2681,10 +2681,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479425</v>
+        <v>479281</v>
       </c>
       <c r="R20" t="n">
-        <v>6723879</v>
+        <v>6723751</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2716,7 +2716,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,7 +2726,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2753,10 +2758,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134165032</v>
+        <v>134165042</v>
       </c>
       <c r="B21" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2788,7 +2793,7 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479337</v>
+        <v>479336</v>
       </c>
       <c r="R21" t="n">
         <v>6723933</v>
@@ -2823,7 +2828,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2833,7 +2838,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2860,10 +2870,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134166446</v>
+        <v>134163861</v>
       </c>
       <c r="B22" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2895,10 +2905,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479281</v>
+        <v>479377</v>
       </c>
       <c r="R22" t="n">
-        <v>6723751</v>
+        <v>6723827</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2930,7 +2940,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2940,12 +2950,12 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC22" t="inlineStr">
         <is>
-          <t>Draperad tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2972,10 +2982,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>134165042</v>
+        <v>134164406</v>
       </c>
       <c r="B23" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3007,10 +3017,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>479336</v>
+        <v>479425</v>
       </c>
       <c r="R23" t="n">
-        <v>6723932</v>
+        <v>6723879</v>
       </c>
       <c r="S23" t="n">
         <v>5</v>
@@ -3042,7 +3052,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3052,12 +3062,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3084,10 +3089,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134163861</v>
+        <v>134165321</v>
       </c>
       <c r="B24" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3119,10 +3124,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479377</v>
+        <v>479298</v>
       </c>
       <c r="R24" t="n">
-        <v>6723827</v>
+        <v>6724027</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3154,7 +3159,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3164,7 +3169,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AC24" t="inlineStr">
@@ -3196,10 +3201,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134165321</v>
+        <v>134165785</v>
       </c>
       <c r="B25" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3231,10 +3236,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479298</v>
+        <v>479393</v>
       </c>
       <c r="R25" t="n">
-        <v>6724027</v>
+        <v>6723974</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3266,7 +3271,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3276,12 +3281,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,10 +3308,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134165230</v>
+        <v>134165032</v>
       </c>
       <c r="B26" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3343,10 +3343,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479282</v>
+        <v>479337</v>
       </c>
       <c r="R26" t="n">
-        <v>6723997</v>
+        <v>6723933</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3378,7 +3378,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3388,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,10 +3415,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134165785</v>
+        <v>134165230</v>
       </c>
       <c r="B27" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3450,10 +3450,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479393</v>
+        <v>479282</v>
       </c>
       <c r="R27" t="n">
-        <v>6723974</v>
+        <v>6723997</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3485,7 +3485,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3495,7 +3495,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3525,7 +3525,7 @@
         <v>134162855</v>
       </c>
       <c r="B28" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3637,7 +3637,7 @@
         <v>134163990</v>
       </c>
       <c r="B29" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>134163684</v>
       </c>
       <c r="B30" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3853,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134163619</v>
+        <v>134162425</v>
       </c>
       <c r="B31" t="n">
-        <v>79359</v>
+        <v>79123</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3864,21 +3864,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3888,10 +3888,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479321</v>
+        <v>479228</v>
       </c>
       <c r="R31" t="n">
-        <v>6723859</v>
+        <v>6723907</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3933,7 +3933,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3963,7 +3963,7 @@
         <v>134163785</v>
       </c>
       <c r="B32" t="n">
-        <v>79116</v>
+        <v>79123</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4067,10 +4067,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134162425</v>
+        <v>134163619</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>79366</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4078,21 +4078,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4102,10 +4102,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479228</v>
+        <v>479321</v>
       </c>
       <c r="R33" t="n">
-        <v>6723907</v>
+        <v>6723859</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4137,7 +4137,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4177,7 +4177,7 @@
         <v>134165466</v>
       </c>
       <c r="B34" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4284,7 +4284,7 @@
         <v>134163648</v>
       </c>
       <c r="B35" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4391,7 +4391,7 @@
         <v>134163276</v>
       </c>
       <c r="B36" t="n">
-        <v>79978</v>
+        <v>79985</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4495,10 +4495,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134163625</v>
+        <v>134164460</v>
       </c>
       <c r="B37" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4530,10 +4530,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479321</v>
+        <v>479403</v>
       </c>
       <c r="R37" t="n">
-        <v>6723861</v>
+        <v>6723893</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4565,7 +4565,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4602,10 +4602,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134164460</v>
+        <v>134164890</v>
       </c>
       <c r="B38" t="n">
-        <v>79359</v>
+        <v>79124</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4613,21 +4613,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4637,10 +4637,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479403</v>
+        <v>479390</v>
       </c>
       <c r="R38" t="n">
-        <v>6723893</v>
+        <v>6723901</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4682,7 +4682,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4821,10 +4821,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134164890</v>
+        <v>134163625</v>
       </c>
       <c r="B40" t="n">
-        <v>79117</v>
+        <v>79366</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4832,21 +4832,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4856,10 +4856,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479390</v>
+        <v>479321</v>
       </c>
       <c r="R40" t="n">
-        <v>6723901</v>
+        <v>6723861</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4891,7 +4891,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4928,10 +4928,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134166374</v>
+        <v>134166742</v>
       </c>
       <c r="B41" t="n">
-        <v>79359</v>
+        <v>57975</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4939,34 +4939,39 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479313</v>
+        <v>479259</v>
       </c>
       <c r="R41" t="n">
-        <v>6723769</v>
+        <v>6723740</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -4998,7 +5003,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5008,7 +5013,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5035,10 +5045,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134166742</v>
+        <v>134166374</v>
       </c>
       <c r="B42" t="n">
-        <v>57975</v>
+        <v>79366</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5046,39 +5056,34 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479259</v>
+        <v>479313</v>
       </c>
       <c r="R42" t="n">
-        <v>6723740</v>
+        <v>6723769</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5110,7 +5115,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5120,12 +5125,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5152,10 +5152,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134163769</v>
+        <v>134166963</v>
       </c>
       <c r="B43" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5187,10 +5187,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479342</v>
+        <v>479288</v>
       </c>
       <c r="R43" t="n">
-        <v>6723828</v>
+        <v>6723786</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5232,7 +5232,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5259,10 +5259,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134166963</v>
+        <v>134163769</v>
       </c>
       <c r="B44" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5294,10 +5294,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479288</v>
+        <v>479342</v>
       </c>
       <c r="R44" t="n">
-        <v>6723786</v>
+        <v>6723828</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5329,7 +5329,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5339,7 +5339,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5603,7 +5603,7 @@
         <v>134164395</v>
       </c>
       <c r="B47" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5707,10 +5707,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134163583</v>
+        <v>134166463</v>
       </c>
       <c r="B48" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5742,10 +5742,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479322</v>
+        <v>479262</v>
       </c>
       <c r="R48" t="n">
-        <v>6723856</v>
+        <v>6723756</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5777,7 +5777,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5787,7 +5787,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5814,10 +5814,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134166463</v>
+        <v>134163583</v>
       </c>
       <c r="B49" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5849,10 +5849,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479262</v>
+        <v>479322</v>
       </c>
       <c r="R49" t="n">
-        <v>6723756</v>
+        <v>6723856</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5884,7 +5884,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5921,10 +5921,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134165072</v>
+        <v>134165087</v>
       </c>
       <c r="B50" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5956,7 +5956,7 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479335</v>
+        <v>479332</v>
       </c>
       <c r="R50" t="n">
         <v>6723933</v>
@@ -6028,45 +6028,50 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134165087</v>
+        <v>134165483</v>
       </c>
       <c r="B51" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479332</v>
+        <v>479354</v>
       </c>
       <c r="R51" t="n">
-        <v>6723933</v>
+        <v>6724019</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6098,7 +6103,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6108,7 +6113,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6135,50 +6140,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134165483</v>
+        <v>134165072</v>
       </c>
       <c r="B52" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479354</v>
+        <v>479335</v>
       </c>
       <c r="R52" t="n">
-        <v>6724019</v>
+        <v>6723933</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6220,7 +6220,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6247,50 +6247,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134166323</v>
+        <v>134162509</v>
       </c>
       <c r="B53" t="n">
-        <v>8460</v>
+        <v>79366</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479371</v>
+        <v>479217</v>
       </c>
       <c r="R53" t="n">
-        <v>6723757</v>
+        <v>6723843</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6322,7 +6317,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6332,7 +6327,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6359,10 +6359,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134167110</v>
+        <v>134163189</v>
       </c>
       <c r="B54" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6394,10 +6394,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479287</v>
+        <v>479248</v>
       </c>
       <c r="R54" t="n">
-        <v>6723832</v>
+        <v>6723888</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6429,7 +6429,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6439,7 +6439,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6466,10 +6466,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134163189</v>
+        <v>134167110</v>
       </c>
       <c r="B55" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6501,10 +6501,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479248</v>
+        <v>479287</v>
       </c>
       <c r="R55" t="n">
-        <v>6723888</v>
+        <v>6723832</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6573,45 +6573,50 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134162509</v>
+        <v>134166323</v>
       </c>
       <c r="B56" t="n">
-        <v>79359</v>
+        <v>8460</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479217</v>
+        <v>479371</v>
       </c>
       <c r="R56" t="n">
-        <v>6723843</v>
+        <v>6723757</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6643,7 +6648,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6653,12 +6658,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>11:06</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6688,7 +6688,7 @@
         <v>134163813</v>
       </c>
       <c r="B57" t="n">
-        <v>79359</v>
+        <v>79366</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6795,7 +6795,7 @@
         <v>134167310</v>
       </c>
       <c r="B58" t="n">
-        <v>79117</v>
+        <v>79124</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>

--- a/artfynd/A 25774-2026 artfynd.xlsx
+++ b/artfynd/A 25774-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY58"/>
+  <dimension ref="A1:AY59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,11 +678,11 @@
         <v>134162456</v>
       </c>
       <c r="B2" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -787,14 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>134164225</v>
+        <v>134162509</v>
       </c>
       <c r="B3" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479428</v>
+        <v>479217</v>
       </c>
       <c r="R3" t="n">
-        <v>6723858</v>
+        <v>6723843</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -857,7 +857,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:06</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -867,7 +867,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>11:06</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -894,14 +899,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>134164290</v>
+        <v>134162699</v>
       </c>
       <c r="B4" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -929,10 +934,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>479422</v>
+        <v>479239</v>
       </c>
       <c r="R4" t="n">
-        <v>6723871</v>
+        <v>6723797</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -964,7 +969,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -974,7 +979,12 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>12:03</t>
+          <t>11:11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1001,14 +1011,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>134165365</v>
+        <v>134162855</v>
       </c>
       <c r="B5" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1036,10 +1046,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>479328</v>
+        <v>479231</v>
       </c>
       <c r="R5" t="n">
-        <v>6723999</v>
+        <v>6723841</v>
       </c>
       <c r="S5" t="n">
         <v>5</v>
@@ -1071,7 +1081,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1081,7 +1091,12 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>12:40</t>
+          <t>11:15</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Tall</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1108,50 +1123,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>134165499</v>
+        <v>134163059</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>479354</v>
+        <v>479292</v>
       </c>
       <c r="R6" t="n">
-        <v>6724019</v>
+        <v>6723887</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1183,7 +1193,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1193,7 +1203,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>11:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1220,14 +1230,14 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>134165773</v>
+        <v>134163189</v>
       </c>
       <c r="B7" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1255,10 +1265,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>479391</v>
+        <v>479248</v>
       </c>
       <c r="R7" t="n">
-        <v>6723987</v>
+        <v>6723888</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1290,7 +1300,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1300,7 +1310,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1327,50 +1337,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>134163699</v>
+        <v>134163583</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>479346</v>
+        <v>479322</v>
       </c>
       <c r="R8" t="n">
-        <v>6723849</v>
+        <v>6723856</v>
       </c>
       <c r="S8" t="n">
         <v>5</v>
@@ -1402,7 +1407,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1412,7 +1417,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>11:41</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1439,50 +1444,45 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>134166414</v>
+        <v>134163607</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>479293</v>
+        <v>479323</v>
       </c>
       <c r="R9" t="n">
-        <v>6723747</v>
+        <v>6723858</v>
       </c>
       <c r="S9" t="n">
         <v>5</v>
@@ -1514,7 +1514,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1524,12 +1524,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>11:37</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Ringhack på tall.</t>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1556,14 +1556,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>134165540</v>
+        <v>134163619</v>
       </c>
       <c r="B10" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1591,10 +1591,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>479345</v>
+        <v>479321</v>
       </c>
       <c r="R10" t="n">
-        <v>6723975</v>
+        <v>6723859</v>
       </c>
       <c r="S10" t="n">
         <v>5</v>
@@ -1626,7 +1626,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1663,14 +1663,14 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>134165475</v>
+        <v>134163625</v>
       </c>
       <c r="B11" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
@@ -1698,10 +1698,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>479353</v>
+        <v>479321</v>
       </c>
       <c r="R11" t="n">
-        <v>6724020</v>
+        <v>6723861</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
@@ -1733,7 +1733,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1743,7 +1743,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1770,14 +1770,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>134165546</v>
+        <v>134163648</v>
       </c>
       <c r="B12" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1805,10 +1805,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>479354</v>
+        <v>479322</v>
       </c>
       <c r="R12" t="n">
-        <v>6723979</v>
+        <v>6723860</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1840,7 +1840,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1850,7 +1850,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>12:50</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1877,14 +1877,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>134164194</v>
+        <v>134163684</v>
       </c>
       <c r="B13" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1912,10 +1912,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>479427</v>
+        <v>479334</v>
       </c>
       <c r="R13" t="n">
-        <v>6723856</v>
+        <v>6723843</v>
       </c>
       <c r="S13" t="n">
         <v>5</v>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1957,12 +1957,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:00</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>11:40</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1989,14 +1984,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>134162699</v>
+        <v>134163769</v>
       </c>
       <c r="B14" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2024,10 +2019,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>479239</v>
+        <v>479342</v>
       </c>
       <c r="R14" t="n">
-        <v>6723797</v>
+        <v>6723828</v>
       </c>
       <c r="S14" t="n">
         <v>5</v>
@@ -2059,7 +2054,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>11:11</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2069,12 +2064,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>11:11</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2101,50 +2091,45 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>134163704</v>
+        <v>134163813</v>
       </c>
       <c r="B15" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>479343</v>
+        <v>479351</v>
       </c>
       <c r="R15" t="n">
-        <v>6723847</v>
+        <v>6723809</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2176,7 +2161,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2186,7 +2171,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>11:42</t>
+          <t>11:48</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2213,14 +2198,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>134163607</v>
+        <v>134163861</v>
       </c>
       <c r="B16" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2248,10 +2233,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>479323</v>
+        <v>479377</v>
       </c>
       <c r="R16" t="n">
-        <v>6723858</v>
+        <v>6723827</v>
       </c>
       <c r="S16" t="n">
         <v>5</v>
@@ -2283,7 +2268,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2293,7 +2278,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>11:51</t>
         </is>
       </c>
       <c r="AC16" t="inlineStr">
@@ -2325,32 +2310,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>134165684</v>
+        <v>134163990</v>
       </c>
       <c r="B17" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2360,10 +2345,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>479369</v>
+        <v>479390</v>
       </c>
       <c r="R17" t="n">
-        <v>6723963</v>
+        <v>6723840</v>
       </c>
       <c r="S17" t="n">
         <v>5</v>
@@ -2395,7 +2380,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:55</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2405,7 +2390,12 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>12:56</t>
+          <t>11:55</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2432,14 +2422,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>134164387</v>
+        <v>134164194</v>
       </c>
       <c r="B18" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2467,10 +2457,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>479421</v>
+        <v>479427</v>
       </c>
       <c r="R18" t="n">
-        <v>6723880</v>
+        <v>6723856</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2502,7 +2492,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2512,7 +2502,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2539,14 +2534,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>134163059</v>
+        <v>134164225</v>
       </c>
       <c r="B19" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2574,10 +2569,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>479292</v>
+        <v>479428</v>
       </c>
       <c r="R19" t="n">
-        <v>6723887</v>
+        <v>6723858</v>
       </c>
       <c r="S19" t="n">
         <v>5</v>
@@ -2609,7 +2604,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2619,7 +2614,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:01</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2646,14 +2641,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>134166446</v>
+        <v>134164290</v>
       </c>
       <c r="B20" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2681,10 +2676,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>479281</v>
+        <v>479422</v>
       </c>
       <c r="R20" t="n">
-        <v>6723751</v>
+        <v>6723871</v>
       </c>
       <c r="S20" t="n">
         <v>5</v>
@@ -2716,7 +2711,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:28</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2726,12 +2721,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:28</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Draperad tall.</t>
+          <t>12:03</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2758,14 +2748,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>134165042</v>
+        <v>134164387</v>
       </c>
       <c r="B21" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2793,10 +2783,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>479336</v>
+        <v>479421</v>
       </c>
       <c r="R21" t="n">
-        <v>6723933</v>
+        <v>6723880</v>
       </c>
       <c r="S21" t="n">
         <v>5</v>
@@ -2828,7 +2818,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12:26</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2838,12 +2828,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>12:26</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2870,14 +2855,14 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>134163861</v>
+        <v>134164395</v>
       </c>
       <c r="B22" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
@@ -2905,10 +2890,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>479377</v>
+        <v>479423</v>
       </c>
       <c r="R22" t="n">
-        <v>6723827</v>
+        <v>6723879</v>
       </c>
       <c r="S22" t="n">
         <v>5</v>
@@ -2940,7 +2925,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11:51</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2950,12 +2935,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>11:51</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>12:06</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2985,11 +2965,11 @@
         <v>134164406</v>
       </c>
       <c r="B23" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
@@ -3089,14 +3069,14 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>134165321</v>
+        <v>134164460</v>
       </c>
       <c r="B24" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
@@ -3124,10 +3104,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>479298</v>
+        <v>479403</v>
       </c>
       <c r="R24" t="n">
-        <v>6724027</v>
+        <v>6723893</v>
       </c>
       <c r="S24" t="n">
         <v>5</v>
@@ -3159,7 +3139,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>12:38</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3169,12 +3149,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>12:38</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3201,14 +3176,14 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>134165785</v>
+        <v>134165032</v>
       </c>
       <c r="B25" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -3236,10 +3211,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>479393</v>
+        <v>479337</v>
       </c>
       <c r="R25" t="n">
-        <v>6723974</v>
+        <v>6723933</v>
       </c>
       <c r="S25" t="n">
         <v>5</v>
@@ -3271,7 +3246,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3281,7 +3256,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>13:03</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3308,14 +3283,14 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>134165032</v>
+        <v>134165042</v>
       </c>
       <c r="B26" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
@@ -3343,10 +3318,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>479337</v>
+        <v>479336</v>
       </c>
       <c r="R26" t="n">
-        <v>6723933</v>
+        <v>6723932</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
@@ -3378,7 +3353,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:26</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3388,7 +3363,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>12:26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3415,14 +3395,14 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>134165230</v>
+        <v>134165072</v>
       </c>
       <c r="B27" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
@@ -3450,10 +3430,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>479282</v>
+        <v>479335</v>
       </c>
       <c r="R27" t="n">
-        <v>6723997</v>
+        <v>6723933</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3485,7 +3465,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3495,7 +3475,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>12:35</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3522,14 +3502,14 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>134162855</v>
+        <v>134165087</v>
       </c>
       <c r="B28" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
@@ -3557,10 +3537,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>479231</v>
+        <v>479332</v>
       </c>
       <c r="R28" t="n">
-        <v>6723841</v>
+        <v>6723933</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3592,7 +3572,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3602,12 +3582,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:15</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Tall</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3634,14 +3609,14 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>134163990</v>
+        <v>134165230</v>
       </c>
       <c r="B29" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
@@ -3669,10 +3644,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>479390</v>
+        <v>479282</v>
       </c>
       <c r="R29" t="n">
-        <v>6723840</v>
+        <v>6723997</v>
       </c>
       <c r="S29" t="n">
         <v>5</v>
@@ -3704,7 +3679,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:55</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3714,12 +3689,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:55</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>12:35</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3746,14 +3716,14 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>134163684</v>
+        <v>134165321</v>
       </c>
       <c r="B30" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -3781,10 +3751,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>479334</v>
+        <v>479298</v>
       </c>
       <c r="R30" t="n">
-        <v>6723843</v>
+        <v>6724027</v>
       </c>
       <c r="S30" t="n">
         <v>5</v>
@@ -3816,7 +3786,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3826,7 +3796,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:40</t>
+          <t>12:38</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3853,32 +3828,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>134162425</v>
+        <v>134165365</v>
       </c>
       <c r="B31" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3888,10 +3863,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>479228</v>
+        <v>479328</v>
       </c>
       <c r="R31" t="n">
-        <v>6723907</v>
+        <v>6723999</v>
       </c>
       <c r="S31" t="n">
         <v>5</v>
@@ -3923,7 +3898,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3933,7 +3908,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:03</t>
+          <t>12:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3960,32 +3935,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>134163785</v>
+        <v>134165466</v>
       </c>
       <c r="B32" t="n">
-        <v>79123</v>
+        <v>79373</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3995,10 +3970,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>479341</v>
+        <v>479354</v>
       </c>
       <c r="R32" t="n">
-        <v>6723828</v>
+        <v>6724022</v>
       </c>
       <c r="S32" t="n">
         <v>5</v>
@@ -4030,7 +4005,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4040,7 +4015,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:45</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4067,14 +4042,14 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>134163619</v>
+        <v>134165475</v>
       </c>
       <c r="B33" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -4102,10 +4077,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>479321</v>
+        <v>479353</v>
       </c>
       <c r="R33" t="n">
-        <v>6723859</v>
+        <v>6724020</v>
       </c>
       <c r="S33" t="n">
         <v>5</v>
@@ -4137,7 +4112,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4147,7 +4122,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4174,14 +4149,14 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>134165466</v>
+        <v>134165540</v>
       </c>
       <c r="B34" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
@@ -4209,10 +4184,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>479354</v>
+        <v>479345</v>
       </c>
       <c r="R34" t="n">
-        <v>6724022</v>
+        <v>6723975</v>
       </c>
       <c r="S34" t="n">
         <v>5</v>
@@ -4244,7 +4219,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4254,7 +4229,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4281,14 +4256,14 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>134163648</v>
+        <v>134165546</v>
       </c>
       <c r="B35" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
@@ -4316,10 +4291,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>479322</v>
+        <v>479354</v>
       </c>
       <c r="R35" t="n">
-        <v>6723860</v>
+        <v>6723979</v>
       </c>
       <c r="S35" t="n">
         <v>5</v>
@@ -4351,7 +4326,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4361,7 +4336,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:50</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4388,32 +4363,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>134163276</v>
+        <v>134165773</v>
       </c>
       <c r="B36" t="n">
-        <v>79985</v>
+        <v>79373</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4423,10 +4398,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>479265</v>
+        <v>479391</v>
       </c>
       <c r="R36" t="n">
-        <v>6723901</v>
+        <v>6723987</v>
       </c>
       <c r="S36" t="n">
         <v>5</v>
@@ -4458,7 +4433,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4468,7 +4443,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4495,14 +4470,14 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>134164460</v>
+        <v>134165785</v>
       </c>
       <c r="B37" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
@@ -4530,10 +4505,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>479403</v>
+        <v>479393</v>
       </c>
       <c r="R37" t="n">
-        <v>6723893</v>
+        <v>6723974</v>
       </c>
       <c r="S37" t="n">
         <v>5</v>
@@ -4565,7 +4540,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4575,7 +4550,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>13:03</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4602,32 +4577,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>134164890</v>
+        <v>134166374</v>
       </c>
       <c r="B38" t="n">
-        <v>79124</v>
+        <v>79373</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4637,10 +4612,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>479390</v>
+        <v>479313</v>
       </c>
       <c r="R38" t="n">
-        <v>6723901</v>
+        <v>6723769</v>
       </c>
       <c r="S38" t="n">
         <v>5</v>
@@ -4672,7 +4647,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4682,7 +4657,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>12:17</t>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4709,50 +4684,45 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>134163763</v>
+        <v>134166446</v>
       </c>
       <c r="B39" t="n">
-        <v>8460</v>
+        <v>79373</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>479344</v>
+        <v>479281</v>
       </c>
       <c r="R39" t="n">
-        <v>6723828</v>
+        <v>6723751</v>
       </c>
       <c r="S39" t="n">
         <v>5</v>
@@ -4784,7 +4754,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:28</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4794,7 +4764,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>13:28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Draperad tall.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4821,14 +4796,14 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>134163625</v>
+        <v>134166463</v>
       </c>
       <c r="B40" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E40" t="n">
@@ -4856,10 +4831,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>479321</v>
+        <v>479262</v>
       </c>
       <c r="R40" t="n">
-        <v>6723861</v>
+        <v>6723756</v>
       </c>
       <c r="S40" t="n">
         <v>5</v>
@@ -4891,7 +4866,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -4901,7 +4876,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4928,50 +4903,45 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>134166742</v>
+        <v>134166963</v>
       </c>
       <c r="B41" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P41" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>479259</v>
+        <v>479288</v>
       </c>
       <c r="R41" t="n">
-        <v>6723740</v>
+        <v>6723786</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
@@ -5003,7 +4973,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>13:39</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5013,12 +4983,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>13:39</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Ringhack på tall.</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5045,14 +5010,14 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>134166374</v>
+        <v>134167110</v>
       </c>
       <c r="B42" t="n">
-        <v>79366</v>
+        <v>79373</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
@@ -5080,10 +5045,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>479313</v>
+        <v>479287</v>
       </c>
       <c r="R42" t="n">
-        <v>6723769</v>
+        <v>6723832</v>
       </c>
       <c r="S42" t="n">
         <v>5</v>
@@ -5115,7 +5080,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5125,7 +5090,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:51</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5152,10 +5117,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>134166963</v>
+        <v>134162323</v>
       </c>
       <c r="B43" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5163,21 +5128,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5187,10 +5152,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>479288</v>
+        <v>479199</v>
       </c>
       <c r="R43" t="n">
-        <v>6723786</v>
+        <v>6723918</v>
       </c>
       <c r="S43" t="n">
         <v>5</v>
@@ -5222,7 +5187,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5232,7 +5197,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>10:57</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5259,10 +5224,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>134163769</v>
+        <v>134162425</v>
       </c>
       <c r="B44" t="n">
-        <v>79366</v>
+        <v>79130</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5270,21 +5235,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5294,10 +5259,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>479342</v>
+        <v>479228</v>
       </c>
       <c r="R44" t="n">
-        <v>6723828</v>
+        <v>6723907</v>
       </c>
       <c r="S44" t="n">
         <v>5</v>
@@ -5329,7 +5294,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5339,7 +5304,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>11:44</t>
+          <t>11:03</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5366,10 +5331,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>134166567</v>
+        <v>134163785</v>
       </c>
       <c r="B45" t="n">
-        <v>57975</v>
+        <v>79130</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5377,39 +5342,34 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>479256</v>
+        <v>479341</v>
       </c>
       <c r="R45" t="n">
-        <v>6723737</v>
+        <v>6723828</v>
       </c>
       <c r="S45" t="n">
         <v>5</v>
@@ -5441,7 +5401,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>13:35</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5451,12 +5411,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>13:35</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack på tall. Bild koda.</t>
+          <t>11:45</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5483,10 +5438,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>134164544</v>
+        <v>134163276</v>
       </c>
       <c r="B46" t="n">
-        <v>57972</v>
+        <v>79992</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5494,39 +5449,34 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P46" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>479407</v>
+        <v>479265</v>
       </c>
       <c r="R46" t="n">
-        <v>6723892</v>
+        <v>6723901</v>
       </c>
       <c r="S46" t="n">
         <v>5</v>
@@ -5558,7 +5508,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>12:08</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5568,12 +5518,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>12:08</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Gran</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5600,10 +5545,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>134164395</v>
+        <v>134165684</v>
       </c>
       <c r="B47" t="n">
-        <v>79366</v>
+        <v>79992</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5611,21 +5556,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5635,10 +5580,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>479423</v>
+        <v>479369</v>
       </c>
       <c r="R47" t="n">
-        <v>6723879</v>
+        <v>6723963</v>
       </c>
       <c r="S47" t="n">
         <v>5</v>
@@ -5670,7 +5615,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5680,7 +5625,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>12:06</t>
+          <t>12:56</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5707,45 +5652,50 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>134166463</v>
+        <v>134163699</v>
       </c>
       <c r="B48" t="n">
-        <v>79366</v>
+        <v>57972</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>479262</v>
+        <v>479346</v>
       </c>
       <c r="R48" t="n">
-        <v>6723756</v>
+        <v>6723849</v>
       </c>
       <c r="S48" t="n">
         <v>5</v>
@@ -5777,7 +5727,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5787,7 +5737,7 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>11:41</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5814,45 +5764,50 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>134163583</v>
+        <v>134164544</v>
       </c>
       <c r="B49" t="n">
-        <v>79366</v>
+        <v>57972</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P49" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>479322</v>
+        <v>479407</v>
       </c>
       <c r="R49" t="n">
-        <v>6723856</v>
+        <v>6723892</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -5884,7 +5839,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:08</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -5894,7 +5849,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:37</t>
+          <t>12:08</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5921,45 +5881,50 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>134165087</v>
+        <v>134165499</v>
       </c>
       <c r="B50" t="n">
-        <v>79366</v>
+        <v>57972</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P50" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>479332</v>
+        <v>479354</v>
       </c>
       <c r="R50" t="n">
-        <v>6723933</v>
+        <v>6724019</v>
       </c>
       <c r="S50" t="n">
         <v>5</v>
@@ -5991,7 +5956,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6001,7 +5966,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6028,38 +5993,38 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>134165483</v>
+        <v>134166414</v>
       </c>
       <c r="B51" t="n">
-        <v>8460</v>
+        <v>57975</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="M51" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6068,10 +6033,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>479354</v>
+        <v>479293</v>
       </c>
       <c r="R51" t="n">
-        <v>6724019</v>
+        <v>6723747</v>
       </c>
       <c r="S51" t="n">
         <v>5</v>
@@ -6103,7 +6068,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6113,7 +6078,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>12:47</t>
+          <t>13:26</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6140,10 +6110,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>134165072</v>
+        <v>134166567</v>
       </c>
       <c r="B52" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6151,34 +6121,39 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>479335</v>
+        <v>479256</v>
       </c>
       <c r="R52" t="n">
-        <v>6723933</v>
+        <v>6723737</v>
       </c>
       <c r="S52" t="n">
         <v>5</v>
@@ -6210,7 +6185,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:35</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6220,7 +6195,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>13:35</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Ringhack på tall. Bild koda.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6247,10 +6227,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>134162509</v>
+        <v>134166742</v>
       </c>
       <c r="B53" t="n">
-        <v>79366</v>
+        <v>57975</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6258,34 +6238,39 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>479217</v>
+        <v>479259</v>
       </c>
       <c r="R53" t="n">
-        <v>6723843</v>
+        <v>6723740</v>
       </c>
       <c r="S53" t="n">
         <v>5</v>
@@ -6317,7 +6302,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6327,12 +6312,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>11:06</t>
+          <t>13:39</t>
         </is>
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Tall</t>
+          <t>Ringhack på tall.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6359,45 +6344,50 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>134163189</v>
+        <v>134163704</v>
       </c>
       <c r="B54" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>479248</v>
+        <v>479343</v>
       </c>
       <c r="R54" t="n">
-        <v>6723888</v>
+        <v>6723847</v>
       </c>
       <c r="S54" t="n">
         <v>5</v>
@@ -6429,7 +6419,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6439,7 +6429,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:42</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6466,45 +6456,50 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>134167110</v>
+        <v>134163763</v>
       </c>
       <c r="B55" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>479287</v>
+        <v>479344</v>
       </c>
       <c r="R55" t="n">
-        <v>6723832</v>
+        <v>6723828</v>
       </c>
       <c r="S55" t="n">
         <v>5</v>
@@ -6536,7 +6531,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6546,7 +6541,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>13:51</t>
+          <t>11:44</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6573,7 +6568,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>134166323</v>
+        <v>134165483</v>
       </c>
       <c r="B56" t="n">
         <v>8460</v>
@@ -6613,10 +6608,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>479371</v>
+        <v>479354</v>
       </c>
       <c r="R56" t="n">
-        <v>6723757</v>
+        <v>6724019</v>
       </c>
       <c r="S56" t="n">
         <v>5</v>
@@ -6648,7 +6643,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6658,7 +6653,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>12:47</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6685,45 +6680,50 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>134163813</v>
+        <v>134166323</v>
       </c>
       <c r="B57" t="n">
-        <v>79366</v>
+        <v>8460</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Gränsberg, Gränsberg, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>479351</v>
+        <v>479371</v>
       </c>
       <c r="R57" t="n">
-        <v>6723809</v>
+        <v>6723757</v>
       </c>
       <c r="S57" t="n">
         <v>5</v>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6765,7 +6765,7 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>11:48</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6792,10 +6792,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134167310</v>
+        <v>134164890</v>
       </c>
       <c r="B58" t="n">
-        <v>79124</v>
+        <v>79131</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6827,10 +6827,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>479227</v>
+        <v>479390</v>
       </c>
       <c r="R58" t="n">
-        <v>6723909</v>
+        <v>6723901</v>
       </c>
       <c r="S58" t="n">
         <v>5</v>
@@ -6862,7 +6862,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -6872,7 +6872,7 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>13:57</t>
+          <t>12:17</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6896,6 +6896,113 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>134167310</v>
+      </c>
+      <c r="B59" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Gränsberg, Gränsberg, Dlr</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>479227</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6723909</v>
+      </c>
+      <c r="S59" t="n">
+        <v>5</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Leksand</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-06-06</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>13:57</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Karl Ericson</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 25774-2026 artfynd.xlsx
+++ b/artfynd/A 25774-2026 artfynd.xlsx
@@ -3321,7 +3321,7 @@
         <v>479336</v>
       </c>
       <c r="R26" t="n">
-        <v>6723932</v>
+        <v>6723933</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 25774-2026 artfynd.xlsx
+++ b/artfynd/A 25774-2026 artfynd.xlsx
@@ -3321,7 +3321,7 @@
         <v>479336</v>
       </c>
       <c r="R26" t="n">
-        <v>6723933</v>
+        <v>6723932</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>

--- a/artfynd/A 25774-2026 artfynd.xlsx
+++ b/artfynd/A 25774-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY59"/>
+  <dimension ref="A1:AZ59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162456</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -896,6 +906,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162509</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1008,6 +1023,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162699</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1120,6 +1140,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162855</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163059</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1334,6 +1364,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163189</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163583</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163607</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1660,6 +1705,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163619</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1767,6 +1817,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163625</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1874,6 +1929,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163648</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1981,6 +2041,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163684</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2088,6 +2153,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163769</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2195,6 +2265,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163813</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2307,6 +2382,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163861</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2419,6 +2499,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163990</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2531,6 +2616,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134164194</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2638,6 +2728,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134164225</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2745,6 +2840,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134164290</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2852,6 +2952,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134164387</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2959,6 +3064,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134164395</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3066,6 +3176,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134164406</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3173,6 +3288,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134164460</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3280,6 +3400,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165032</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3392,6 +3517,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165042</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3499,6 +3629,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165072</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3606,6 +3741,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165087</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3713,6 +3853,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165230</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3825,6 +3970,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165321</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3932,6 +4082,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165365</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4039,6 +4194,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165466</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4146,6 +4306,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165475</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4253,6 +4418,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165540</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4360,6 +4530,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165546</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4467,6 +4642,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165773</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4574,6 +4754,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165785</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4681,6 +4866,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166374</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4793,6 +4983,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166446</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4900,6 +5095,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166463</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5007,6 +5207,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166963</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5114,6 +5319,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134167110</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5221,6 +5431,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162323</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5328,6 +5543,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134162425</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5435,6 +5655,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163785</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5542,6 +5767,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163276</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5649,6 +5879,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165684</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5761,6 +5996,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163699</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5878,6 +6118,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134164544</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5990,6 +6235,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165499</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -6107,6 +6357,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166414</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6224,6 +6479,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166567</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6341,6 +6601,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166742</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6453,6 +6718,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163704</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6565,6 +6835,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134163763</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6677,6 +6952,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134165483</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6789,6 +7069,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134166323</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6896,6 +7181,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134164890</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -7003,8 +7293,73 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134167310</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>